--- a/subclass neurotransmitters.xlsx
+++ b/subclass neurotransmitters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpv88\Documents\GitHub\HCRprocess\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C993DD6-296A-4F4A-BF16-DAC702995A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74ABAB3-80DC-4655-B027-D1E71A0A4238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>Vglut</t>
   </si>
@@ -148,6 +148,21 @@
   </si>
   <si>
     <t>308 DCO Il22 Gly-Gaba</t>
+  </si>
+  <si>
+    <t>nt group</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>cht</t>
+  </si>
+  <si>
+    <t>vglut</t>
+  </si>
+  <si>
+    <t>vgat</t>
   </si>
 </sst>
 </file>
@@ -465,13 +480,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -481,8 +496,11 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -495,8 +513,11 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -509,8 +530,11 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -523,8 +547,11 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -537,8 +564,11 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -551,8 +581,11 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -565,8 +598,11 @@
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -579,8 +615,11 @@
       <c r="D8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -593,8 +632,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -607,8 +649,11 @@
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -621,8 +666,11 @@
       <c r="D11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -635,8 +683,11 @@
       <c r="D12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -649,8 +700,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -663,8 +717,11 @@
       <c r="D14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -677,8 +734,11 @@
       <c r="D15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -691,8 +751,11 @@
       <c r="D16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -705,8 +768,11 @@
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -719,8 +785,11 @@
       <c r="D18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -733,8 +802,11 @@
       <c r="D19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -747,8 +819,11 @@
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -761,8 +836,11 @@
       <c r="D21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -775,8 +853,11 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -789,8 +870,11 @@
       <c r="D23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -803,8 +887,11 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -817,8 +904,11 @@
       <c r="D25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -831,8 +921,11 @@
       <c r="D26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -845,8 +938,11 @@
       <c r="D27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -859,8 +955,11 @@
       <c r="D28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -873,8 +972,11 @@
       <c r="D29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -887,8 +989,11 @@
       <c r="D30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -901,8 +1006,11 @@
       <c r="D31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -915,8 +1023,11 @@
       <c r="D32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -929,8 +1040,11 @@
       <c r="D33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -943,8 +1057,11 @@
       <c r="D34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -957,8 +1074,11 @@
       <c r="D35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -971,8 +1091,11 @@
       <c r="D36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -985,8 +1108,11 @@
       <c r="D37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -999,8 +1125,11 @@
       <c r="D38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1012,6 +1141,9 @@
       </c>
       <c r="D39">
         <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
